--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Se" sheetId="1" r:id="rId1"/>
@@ -150,10 +150,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -165,72 +165,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,6 +187,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -254,15 +212,89 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,38 +307,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -317,187 +317,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,17 +511,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,11 +535,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -554,7 +554,33 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,34 +603,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,106 +616,133 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -724,37 +751,10 @@
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -150,10 +150,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -161,20 +161,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -186,19 +172,68 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -210,91 +245,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -307,6 +260,53 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -317,187 +317,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,6 +521,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -535,6 +550,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -545,6 +569,21 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -569,45 +608,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -616,145 +616,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Id</t>
   </si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>gamestart</t>
+  </si>
+  <si>
+    <t>ARTIFACT</t>
+  </si>
+  <si>
+    <t>soundlogo1</t>
+  </si>
+  <si>
+    <t>ALERT</t>
+  </si>
+  <si>
+    <t>decide_13</t>
   </si>
 </sst>
 </file>
@@ -150,9 +162,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -164,6 +176,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -172,13 +228,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -187,51 +259,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,6 +282,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -263,46 +299,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,13 +329,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,169 +431,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,7 +527,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -531,6 +543,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -559,21 +591,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -589,22 +606,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,15 +628,15 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -634,127 +646,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1110,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -1473,6 +1485,40 @@
         <v>1</v>
       </c>
     </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Se" sheetId="1" r:id="rId1"/>
@@ -164,8 +164,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -177,44 +177,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,43 +237,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -273,14 +245,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -289,17 +282,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -307,14 +307,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,13 +329,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,43 +467,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,121 +479,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,6 +520,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -549,44 +564,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,6 +586,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -620,6 +609,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -628,145 +628,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -783,12 +783,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1428,7 +1428,7 @@
         <v>15</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E18">
         <v>1</v>
